--- a/E/BAK02D.xlsx
+++ b/E/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="306">
   <si>
     <t/>
   </si>
@@ -736,6 +736,12 @@
     <t>MR.BRD KSR CHO BNANA</t>
   </si>
   <si>
+    <t>20041084</t>
+  </si>
+  <si>
+    <t>MR.BRD KSR PD COK SR</t>
+  </si>
+  <si>
     <t>20139188</t>
   </si>
   <si>
@@ -863,15 +869,6 @@
   </si>
   <si>
     <t>16</t>
-  </si>
-  <si>
-    <t>20135611</t>
-  </si>
-  <si>
-    <t>PRM.BREAD KRM GL.ARN</t>
-  </si>
-  <si>
-    <t>17</t>
   </si>
   <si>
     <t>20100667</t>
@@ -3569,7 +3566,7 @@
         <v>123</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3589,7 +3586,7 @@
         <v>123</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3606,10 +3603,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3629,7 +3626,7 @@
         <v>126</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3649,7 +3646,7 @@
         <v>126</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3669,7 +3666,7 @@
         <v>126</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3689,7 +3686,7 @@
         <v>126</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3709,7 +3706,7 @@
         <v>126</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3726,10 +3723,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3749,7 +3746,7 @@
         <v>129</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3769,7 +3766,7 @@
         <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3789,7 +3786,7 @@
         <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3809,7 +3806,7 @@
         <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3829,7 +3826,7 @@
         <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3849,7 +3846,7 @@
         <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3869,7 +3866,7 @@
         <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3889,7 +3886,7 @@
         <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3909,7 +3906,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3929,7 +3926,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3949,7 +3946,7 @@
         <v>129</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -3969,7 +3966,7 @@
         <v>129</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>283</v>
+        <v>132</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -3977,10 +3974,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -3989,7 +3986,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -3997,10 +3994,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4009,7 +4006,7 @@
         <v>129</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4017,10 +4014,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4029,7 +4026,7 @@
         <v>129</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4037,10 +4034,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4049,7 +4046,7 @@
         <v>129</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4057,16 +4054,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>4</v>
@@ -4077,16 +4074,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>8</v>
@@ -4097,16 +4094,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>11</v>
@@ -4117,16 +4114,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>14</v>
@@ -4137,16 +4134,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>17</v>

--- a/E/BAK02D.xlsx
+++ b/E/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="293">
   <si>
     <t/>
   </si>
@@ -796,54 +796,24 @@
     <t>PRM BREAD COOKIES</t>
   </si>
   <si>
-    <t>20100666</t>
-  </si>
-  <si>
-    <t>P/BRD DUO CS.PSG&amp;COK</t>
-  </si>
-  <si>
     <t>20125697</t>
   </si>
   <si>
     <t>PRM.BREAD PRM/C CKLT</t>
   </si>
   <si>
-    <t>20125806</t>
-  </si>
-  <si>
-    <t>PRM.BRAD PRM/C TRMSU</t>
-  </si>
-  <si>
     <t>20134325</t>
   </si>
   <si>
     <t>PRM.BREAD COKLAT KCG</t>
   </si>
   <si>
-    <t>20134324</t>
-  </si>
-  <si>
-    <t>PRM.BREAD UBI UNGU</t>
-  </si>
-  <si>
-    <t>20132629</t>
-  </si>
-  <si>
-    <t>PRM.BREAD COCOPANDAN</t>
-  </si>
-  <si>
     <t>20134980</t>
   </si>
   <si>
     <t>PRM.BREAD KRM SRIKY</t>
   </si>
   <si>
-    <t>20070038</t>
-  </si>
-  <si>
-    <t>PRM.BREAD KRM JG.MNS</t>
-  </si>
-  <si>
     <t>20070039</t>
   </si>
   <si>
@@ -887,15 +857,6 @@
   </si>
   <si>
     <t>19</t>
-  </si>
-  <si>
-    <t>20140797</t>
-  </si>
-  <si>
-    <t>PRIME.BR KRM NASTAR</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
   <si>
     <t>20022721</t>
@@ -1321,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3766,7 +3727,7 @@
         <v>129</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3786,7 +3747,7 @@
         <v>129</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3806,7 +3767,7 @@
         <v>129</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3826,7 +3787,7 @@
         <v>129</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3846,7 +3807,7 @@
         <v>129</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3866,7 +3827,7 @@
         <v>129</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3886,7 +3847,7 @@
         <v>129</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>27</v>
+        <v>275</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3894,10 +3855,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -3906,7 +3867,7 @@
         <v>129</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>120</v>
+        <v>278</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3914,10 +3875,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -3926,7 +3887,7 @@
         <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>123</v>
+        <v>281</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3934,221 +3895,101 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>285</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>288</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>291</v>
+        <v>17</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F141" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/E/BAK02D.xlsx
+++ b/E/BAK02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="295">
   <si>
     <t/>
   </si>
@@ -169,6 +169,15 @@
     <t>10</t>
   </si>
   <si>
+    <t>20143387</t>
+  </si>
+  <si>
+    <t>5DAYS MN CROI STR128</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>20003591</t>
   </si>
   <si>
@@ -371,9 +380,6 @@
   </si>
   <si>
     <t>SR/RT SBK DUO SKY 72</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>20125604</t>
@@ -1282,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1684,21 +1690,21 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1707,7 +1713,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1715,10 +1721,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1727,7 +1733,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1735,10 +1741,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1747,7 +1753,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1755,10 +1761,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1767,7 +1773,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1775,10 +1781,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1787,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1795,10 +1801,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1807,7 +1813,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1815,19 +1821,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1835,10 +1841,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1847,7 +1853,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1855,10 +1861,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1867,7 +1873,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1875,10 +1881,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1887,7 +1893,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1895,10 +1901,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1907,7 +1913,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1915,10 +1921,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1927,7 +1933,7 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1935,10 +1941,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1947,7 +1953,7 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1955,10 +1961,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1967,7 +1973,7 @@
         <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1975,19 +1981,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1995,10 +2001,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2007,7 +2013,7 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2015,10 +2021,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2027,7 +2033,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2035,10 +2041,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2047,7 +2053,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -2055,10 +2061,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2067,7 +2073,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2075,10 +2081,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2087,7 +2093,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2095,10 +2101,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2107,7 +2113,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -2115,10 +2121,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2127,7 +2133,7 @@
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2135,19 +2141,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -2155,10 +2161,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2167,7 +2173,7 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -2175,10 +2181,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2187,7 +2193,7 @@
         <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2195,10 +2201,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2207,7 +2213,7 @@
         <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2215,10 +2221,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2227,7 +2233,7 @@
         <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2235,10 +2241,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2247,7 +2253,7 @@
         <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2255,10 +2261,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2267,7 +2273,7 @@
         <v>20</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2275,10 +2281,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2287,7 +2293,7 @@
         <v>20</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2295,10 +2301,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2307,7 +2313,7 @@
         <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2315,10 +2321,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2327,7 +2333,7 @@
         <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2335,10 +2341,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2347,7 +2353,7 @@
         <v>20</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2367,7 +2373,7 @@
         <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2375,10 +2381,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2387,7 +2393,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2395,10 +2401,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2407,7 +2413,7 @@
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2415,10 +2421,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2427,7 +2433,7 @@
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2435,19 +2441,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2507,7 +2513,7 @@
         <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2567,7 +2573,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2627,7 +2633,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2687,7 +2693,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2747,7 +2753,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2787,7 +2793,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2847,7 +2853,7 @@
         <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2887,7 +2893,7 @@
         <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2944,10 +2950,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2967,7 +2973,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2987,7 +2993,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3004,10 +3010,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3027,7 +3033,7 @@
         <v>48</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3047,7 +3053,7 @@
         <v>48</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3067,7 +3073,7 @@
         <v>48</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3087,7 +3093,7 @@
         <v>48</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3104,10 +3110,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3127,7 +3133,7 @@
         <v>51</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3147,7 +3153,7 @@
         <v>51</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3167,7 +3173,7 @@
         <v>51</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3187,7 +3193,7 @@
         <v>51</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3207,7 +3213,7 @@
         <v>51</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3227,7 +3233,7 @@
         <v>51</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3247,7 +3253,7 @@
         <v>51</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3264,10 +3270,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3284,10 +3290,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3304,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3324,13 +3330,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3344,10 +3350,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3364,10 +3370,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3384,10 +3390,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3404,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3424,10 +3430,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3444,10 +3450,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3464,10 +3470,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3484,10 +3490,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3504,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3524,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3544,10 +3550,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3564,10 +3570,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3584,10 +3590,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3604,10 +3610,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3624,10 +3630,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3644,10 +3650,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3664,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3684,10 +3690,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3704,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3724,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3744,10 +3750,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3764,10 +3770,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -3784,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3804,10 +3810,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -3824,10 +3830,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -3844,10 +3850,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>275</v>
+        <v>134</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -3855,19 +3861,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -3875,19 +3881,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -3895,39 +3901,39 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E131" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F131" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>21</v>
@@ -3944,10 +3950,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>21</v>
@@ -3964,10 +3970,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>21</v>
@@ -3984,12 +3990,32 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E136" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F136" s="1" t="s">
         <v>21</v>
       </c>
     </row>
